--- a/combat tracker.xlsx
+++ b/combat tracker.xlsx
@@ -52,6 +52,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Adult Green Dragon" sheetId="44" state="visible" r:id="rId44"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Adult Black Dragon" sheetId="45" state="visible" r:id="rId45"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Adult White Dragon" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Korvath Stonehorn" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Varka Ashstride" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sseskari Reed-Speaker" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tharok Ghostclaw" sheetId="50" state="visible" r:id="rId50"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -726,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" style="18" min="1" max="1"/>
@@ -2276,6 +2280,126 @@
       <c r="H52" t="inlineStr">
         <is>
           <t>Dragon — adult white (CR 13) — BOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>NPC</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Korvath Stonehorn</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Korvath Stonehorn</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Panagog Trial boss — Shield of the Circle. Tanks center; PRIORITY: protects Sseskari.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>NPC</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Varka Ashstride</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Varka Ashstride</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Panagog Trial boss — Knife on the Wind. Mobile skirmisher; flanks and switches targets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>NPC</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Sseskari Reed-Speaker</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Sseskari Reed-Speaker</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Panagog Trial boss — Voice Beneath the Stone. Healer/controller; kill or silence to stop support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>NPC</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Tharok Ghostclaw</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Tharok Ghostclaw</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Trial I solo boss — The Thorn King. May be magically controlled (see Traits); ambush predator.</t>
         </is>
       </c>
     </row>
@@ -22599,6 +22723,1751 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>CREATURE STAT BLOCK</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="K2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Korvath Stonehorn</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Epithet</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Shield of the Circle</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Minotaur Heavy Warrior — tank / front-liner</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Size / Type / Alignment</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Large monstrosity, lawful neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Base HP</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>40 ft.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Proficiency Bonus</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Initiative Mod</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ABILITY SCORES</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DEX</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CON</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>WIS</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>22</v>
+      </c>
+      <c r="C15" t="n">
+        <v>12</v>
+      </c>
+      <c r="D15" t="n">
+        <v>20</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="n">
+        <v>14</v>
+      </c>
+      <c r="G15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Modifier</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Save Proficient</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Save Bonus</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DEFENSES &amp; SENSES</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Resistances</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Immunities</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Condition Immunities</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senses</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>darkvision 60 ft., passive Perception 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ATTACKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>To Hit</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Reach / Range</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Save</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Warhammer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Melee Weapon</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>10</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>10 ft.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2d8+6 bludgeoning</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Horn Bash</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Melee Weapon</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>10</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>5 ft.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2d6+6 piercing</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>DC 18 STR</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>On a failed save, target is pushed 10 ft. or knocked prone (Korvath's choice).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Driving Charge</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Special (Recharge 5-6)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Speed, in a line</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>4d10+5 bludgeoning</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>DC 18 DEX</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Korvath moves up to his speed in a straight line without provoking opportunity attacks, and may move through the space of one Large or smaller creature. That creature takes damage and falls prone on a failed save, or takes half damage on a success.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TRAITS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Multiattack</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Korvath makes two Warhammer attacks and one Horn Bash attack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Indomitable (1/Day)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Korvath rerolls a failed saving throw.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Guardian's Reach</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>A creature provokes an opportunity attack from Korvath when it moves from a space within 10 feet of him to another space within 10 feet of him.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Stand Over the Fallen</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Allies within 5 feet of Korvath have half cover. A prone or unconscious ally in that area has three-quarters cover.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Relentless (1/Day)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>If reduced to 0 hit points but not killed outright, Korvath drops to 1 hit point instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Languages</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Common, Giant, Panagog</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Tactics</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Takes the center and physically blocks access to Sseskari. Uses Horn Bash to separate a melee threat from a mage or artificer, then holds the gap. Spends actions shoving, blocking, or protecting rather than maximizing damage. If an ally falls, moves over them and demands space for surrender or healing. Never attacks a yielded foe; only attacks an unconscious foe if it keeps returning as an active threat. Demeanor: quiet, formal, steady — respects anyone who holds position to protect another. Yields if both allies are removed and he is below 40 HP, or if continuing would abandon a dying companion; accepts surrender immediately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>REACTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Interpose Shield</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>When a creature Korvath can see attacks an ally within 5 feet of him, he imposes disadvantage on the attack roll.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>CREATURE STAT BLOCK</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="K2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Varka Ashstride</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Epithet</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Knife on the Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Orc Mobile Warrior — skirmisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Size / Type / Alignment</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Medium humanoid (orc), chaotic neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Base HP</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>45 ft.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Proficiency Bonus</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Initiative Mod</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ABILITY SCORES</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DEX</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CON</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>WIS</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>22</v>
+      </c>
+      <c r="D15" t="n">
+        <v>16</v>
+      </c>
+      <c r="E15" t="n">
+        <v>11</v>
+      </c>
+      <c r="F15" t="n">
+        <v>14</v>
+      </c>
+      <c r="G15" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Modifier</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Save Proficient</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Save Bonus</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DEFENSES &amp; SENSES</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Resistances</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Immunities</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Condition Immunities</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senses</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>passive Perception 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ATTACKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>To Hit</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Reach / Range</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Save</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ashfang</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Melee Weapon</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>10</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>5 ft.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1d8+6 slashing</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Plus 7 (2d6) damage if Varka moved at least 15 feet before the attack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Shortbow</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ranged Weapon</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>10</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>80/320 ft.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1d6+6 piercing</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Hamstring Cut</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Special (Recharge 5-6)</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>10</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>5 ft.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2d8+6 slashing</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>DC 17 CON</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>On a failed save, target's speed is reduced to 0 until the end of its next turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TRAITS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Multiattack</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Varka makes three attacks with Ashfang or her shortbow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Evasion</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>If Varka succeeds on a Dexterity save for half damage, she instead takes no damage; on a failure, she takes half damage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Mobile Assault</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Varka does not provoke opportunity attacks from a creature she has attacked during the same turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Skirmisher</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>When an enemy ends its turn within 5 feet of Varka, she may move up to 15 feet as a reaction without provoking opportunity attacks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Uncanny Dodge</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Varka halves the damage from one attack that hits her, provided she can see the attacker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Whirl Through the Line (1/Day)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Varka moves up to her speed without provoking opportunity attacks and may make one Ashfang attack against up to three different creatures she moves adjacent to during this movement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Languages</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Common, Orc, Panagog</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Tactics</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Flanks widely and pressures the mage first, unless the artificer is maintaining a dangerous concentration effect. Uses movement to force the party to split attention; doesn't stay beside the fighter unless trapped. Threatens fallen opponents to force hard choices, but prefers demanding surrender over striking them. Switches targets often to test whether the party protects one another; if Korvath pins a target, she attacks someone else instead of dogpiling (unless the party is dominating). Demeanor: sharp-tongued, competitive, delighted by capable opponents — her taunts challenge courage, not identity. Rarely yields alone; obeys a team surrender from Sseskari or Korvath. If last standing below 25 HP, offers the party one final chance to accept her surrender before a reckless final attack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BONUS ACTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Cunning Action</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Varka takes the Dash, Disengage, or Hide action.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>CREATURE STAT BLOCK</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sseskari Reed-Speaker</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Epithet</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Voice Beneath the Stone</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Lizardfolk Shaman — healer / controller</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Size / Type / Alignment</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Medium humanoid (lizardfolk), neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Base HP</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>30 ft., swim 30 ft.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Proficiency Bonus</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Initiative Mod</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ABILITY SCORES</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DEX</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CON</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>WIS</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="n">
+        <v>14</v>
+      </c>
+      <c r="D15" t="n">
+        <v>18</v>
+      </c>
+      <c r="E15" t="n">
+        <v>13</v>
+      </c>
+      <c r="F15" t="n">
+        <v>20</v>
+      </c>
+      <c r="G15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Modifier</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Save Proficient</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Save Bonus</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>9</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DEFENSES &amp; SENSES</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Resistances</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Immunities</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Condition Immunities</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senses</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>passive Perception 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ATTACKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>To Hit</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Reach / Range</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Save</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Stonekeeper's Staff</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Melee Weapon</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>6</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>5 ft.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1d8+3 bludgeoning plus 2d8 radiant</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Binding Reeds</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Special (Recharge 5-6)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>60 ft. (20-ft. radius)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>DC 17 STR</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Roots and spectral reeds fill a 20-foot-radius area within 60 feet until the end of Sseskari's next turn. The area is difficult terrain. Each enemy entering or starting there must succeed on the save or be restrained until the end of its turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TRAITS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>War Priest's Focus</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Sseskari has advantage on Constitution saves made to maintain concentration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Measured Mercy</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>When Sseskari restores hit points to a creature at 0 hit points, that creature may immediately stand without spending movement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Spellcasting</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>12th-level spellcaster. Spell save DC 17, +9 to hit with spell attacks. Requires no material components except those with a listed cost. Cantrips (at will): guidance, sacred flame, thorn whip, toll the dead. 1st (4 slots): healing word, sanctuary, shield of faith. 2nd (3 slots): lesser restoration, silence, spiritual weapon. 3rd (3 slots): dispel magic, mass healing word, spirit guardians. 4th (3 slots): banishment, freedom of movement, guardian of faith. 5th (2 slots): greater restoration, mass cure wounds. 6th (1 slot): heal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Languages</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Common, Draconic, Panagog</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Tactics</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Begins with spirit guardians only if the party closes aggressively; otherwise uses shield of faith or Binding Reeds. Uses silence against the mage only when it creates an interesting positional problem, not as a permanent shutdown. Prioritizes mass healing word to return an ally to the fight, then heal if a champion is near death. Uses banishment to create a temporary numbers advantage, usually targeting the fighter or artificer rather than the mage. Calls the team surrender when defeat is clear — never sacrifices an ally merely to prolong the trial. Demeanor: calm, observant; treats combat as sacred judgment and announces especially dangerous magic in Panagog before casting. Yields when both allies are down and cannot be restored safely, or when one ally is dying and continued combat would prevent aid — clear, formal, immediate. Team coordination: Korvath holds the center, Varka circles, Sseskari controls lanes and restores allies; they pressure but avoid eliminating one player before that character has meaningful choices. If the party struggles badly by round 3, shift the trio toward grapples, shoves, and surrender demands rather than lethal focus fire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>REACTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Turn the Blow (3/Day)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>When an ally within 30 feet takes damage, Sseskari reduces that damage by 12 (2d6 + 5).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -23060,6 +24929,615 @@
       <c r="B38" t="inlineStr">
         <is>
           <t>Ready a reaction attack vs. next creature moving within 5 ft. without Disengage. Triggers one Spear Strike as a reaction.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>CREATURE STAT BLOCK</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="K2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Tharok Ghostclaw</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Epithet</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>The Thorn King (Trial I)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Apex Predator — solo boss</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Size / Type / Alignment</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Huge monstrosity</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Base HP</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>50 ft., climb 20 ft.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Proficiency Bonus</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Initiative Mod</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ABILITY SCORES</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DEX</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CON</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>WIS</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>24</v>
+      </c>
+      <c r="C15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D15" t="n">
+        <v>19</v>
+      </c>
+      <c r="E15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" t="n">
+        <v>17</v>
+      </c>
+      <c r="G15" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Modifier</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>7</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Save Proficient</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Save Bonus</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>12</v>
+      </c>
+      <c r="C18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D18" t="n">
+        <v>9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>8</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DEFENSES &amp; SENSES</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Resistances</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Immunities</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Condition Immunities</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senses</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>darkvision 120 ft., tremorsense 30 ft., passive Perception 18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ATTACKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>To Hit</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Reach / Range</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Save</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Bite</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Melee Weapon</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>12</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>10 ft.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>3d12+7 piercing</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>DC 18 STR</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>On a failed save, target is grappled and restrained (escape DC 18).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Claw</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Melee Weapon</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>12</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>10 ft.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>3d8+7 slashing</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Tail Sweep</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>15-ft. cone</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2d10+7 bludgeoning</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>DC 18 DEX</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Each creature in the area is knocked prone on a failed save.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Terrifying Roar</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Special (Recharge 5-6)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>90 ft.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>DC 17 WIS</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Each creature that fails is frightened for 1 minute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TRAITS</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Multiattack</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Tharok makes one Bite attack and two Claw attacks (or replaces one Claw with a Tail Sweep).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Ghostscale Camouflage</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Invisible while motionless in natural cover. Invisibility ends when it moves or attacks. After moving through foliage, Tharok may Hide as a bonus action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Apex Senses</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Advantage on Perception and Survival checks that rely on scent; detects bleeding creatures within 60 ft.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Patient Predator</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Tharok has advantage on initiative rolls. During the first round of combat, its movement doesn't provoke opportunity attacks from creatures that haven't yet acted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Legendary Resistance (2/Day)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>If Tharok fails a saving throw, it can choose to succeed instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Legendary Actions (3/round)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Tharok can take 3 legendary actions, choosing from the options below. Only one legendary action can be used at a time and only at the end of another creature's turn. Tharok regains spent legendary actions at the start of its turn. Stalk (move up to half speed); Detect (makes a Wisdom (Perception) check); Claw (costs 1 action, one Claw attack); Ghoststep (costs 2 actions, moves up to full speed and can Hide); Savage Reversal (costs 2 actions, makes one Bite or Tail Sweep attack).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Behavior &amp; Control</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Natural: stalks, ambushes, uses terrain, withdraws if badly outnumbered, defends territory, avoids unnecessary risk. Controlled: magically compelled to relentlessly pursue a designated target, ignores escape opportunities, fights beyond normal limits, and abandons normal hunting instincts. Signs of Control: arcane brand beneath damaged scales, magical flashes beneath skin, unnatural fixation on one victim, refusal to retreat, obvious pain when commands are issued. Ending the Control: dispel magic (5th-level effect), remove or destroy the control focus, break the controller's concentration, or use appropriate restorative magic. Once freed, Tharok is stunned for 1 round before attempting to flee.</t>
         </is>
       </c>
     </row>
